--- a/artfynd/A 60746-2025 artfynd.xlsx
+++ b/artfynd/A 60746-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY3"/>
+  <dimension ref="A1:AY7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,62 +675,52 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>92446348</v>
+        <v>13671799</v>
       </c>
       <c r="B2" t="n">
-        <v>39582</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>6328</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>101166</v>
+        <v>100577</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Mindre träfjäril</t>
+          <t>Tallgångbagge</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Acossus terebra</t>
+          <t>Cerylon impressum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Denis &amp; Schiffermüller, 1775)</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr"/>
-      <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N2" t="inlineStr"/>
+          <t>Erichson, 1845</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Tallskog utmed Ruggtorpsvägen, Sm</t>
+          <t>Ruggstorp SV, Sm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>568140.710074658</v>
+        <v>568198</v>
       </c>
       <c r="R2" t="n">
-        <v>6307632.644828281</v>
+        <v>6307588</v>
       </c>
       <c r="S2" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -754,22 +744,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2021-04-15</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2008-07-23</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2021-04-15</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2008-07-23</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -778,34 +758,43 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
-      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
+      </c>
+      <c r="AI2" t="inlineStr">
+        <is>
+          <t>u bark död tall i vägkant</t>
+        </is>
+      </c>
+      <c r="AQ2" t="inlineStr">
+        <is>
+          <t>Niklas Franc</t>
+        </is>
+      </c>
+      <c r="AR2" t="inlineStr">
+        <is>
+          <t>NF9906</t>
+        </is>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Pontus Axén</t>
+          <t>Niklas Franc</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Pontus Axén, Jonas Hedin</t>
+          <t>Niklas Franc</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>104507686</v>
+        <v>92446348</v>
       </c>
       <c r="B3" t="n">
-        <v>39582</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>40267</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -834,18 +823,22 @@
       <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Nybro, Sm</t>
+          <t>Tallskog utmed Ruggtorpsvägen, Sm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>568284.199703968</v>
+        <v>568141</v>
       </c>
       <c r="R3" t="n">
-        <v>6307958.256396534</v>
+        <v>6307633</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -872,27 +865,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2022-10-18</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>15:53</t>
+          <t>2021-04-15</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2022-10-18</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>15:53</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Sav som runnit på asp. Kurs med Gunnar Isaksson</t>
+          <t>2021-04-15</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -908,15 +886,493 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
+          <t>Pontus Axén</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>Pontus Axén, Jonas Hedin</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>104507686</v>
+      </c>
+      <c r="B4" t="n">
+        <v>40267</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>101166</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Mindre träfjäril</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Acossus terebra</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(Denis &amp; Schiffermüller, 1775)</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr"/>
+      <c r="N4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Nybro, Sm</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>568284</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6307958</v>
+      </c>
+      <c r="S4" t="n">
+        <v>25</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Nybro</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Bäckebo</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2022-10-18</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>15:53</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2022-10-18</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>15:53</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Sav som runnit på asp. Kurs med Gunnar Isaksson</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF4" t="inlineStr"/>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
           <t>Anna-Stina Duerden</t>
         </is>
       </c>
-      <c r="AX3" t="inlineStr">
+      <c r="AX4" t="inlineStr">
         <is>
           <t>Anna-Stina Duerden</t>
         </is>
       </c>
-      <c r="AY3" t="inlineStr"/>
+      <c r="AY4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>86646249</v>
+      </c>
+      <c r="B5" t="n">
+        <v>5394</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>101199</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Hårig blombock</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Etorofus pubescens</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(Fabricius, 1787)</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>imago/adult</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Rugstorpsvägen 2, Sm</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>568199</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6307579</v>
+      </c>
+      <c r="S5" t="n">
+        <v>25</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Nybro</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Bäckebo</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2020-07-03</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2020-07-03</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF5" t="inlineStr"/>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Björn Johansson</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Björn Johansson, Ing-Mari  Frösemo</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>94430110</v>
+      </c>
+      <c r="B6" t="n">
+        <v>5394</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>101199</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Hårig blombock</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Etorofus pubescens</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(Fabricius, 1787)</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr"/>
+      <c r="N6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Rugstorp SV, Sm</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>568221</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6307602</v>
+      </c>
+      <c r="S6" t="n">
+        <v>10</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Nybro</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Bäckebo</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2021-06-22</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2021-06-22</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF6" t="inlineStr"/>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Otto Bylén Claesson</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Otto Bylén Claesson</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>94722843</v>
+      </c>
+      <c r="B7" t="n">
+        <v>5471</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>101377</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Stekelbock</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Necydalis major</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr"/>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>imago/adult</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>frispringande/krypande</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Parkeringsficka med Salix (korr), Sm</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>568196</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6307571</v>
+      </c>
+      <c r="S7" t="n">
+        <v>25</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Nybro</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Bäckebo</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2021-07-06</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>17:30</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2021-07-06</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>18:00</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Satt på en ganska liten/tunn savande sälg som även hade en gammal skada</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF7" t="inlineStr"/>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Carl Tamario</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Carl Tamario, Tobias Berger, Joakim Holm, Oscar Nordahl</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 60746-2025 artfynd.xlsx
+++ b/artfynd/A 60746-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY7"/>
+  <dimension ref="A1:AZ7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -788,6 +793,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/13671799</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -895,6 +905,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/92446348</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1013,6 +1028,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104507686</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1132,6 +1152,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/86646249</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1239,6 +1264,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/94430110</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1373,8 +1403,21 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/94722843</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>